--- a/output/full_scan/batch_seq0_2026-06-23.xlsx
+++ b/output/full_scan/batch_seq0_2026-06-23.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O116"/>
+  <dimension ref="A1:O117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1269,21 +1269,21 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8081</v>
+        <v>8454</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>695.8836098282997</v>
+        <v>700.7486541667641</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>62.92047720186238</v>
+        <v>57.40891596890565</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>30.62459569811681</v>
+        <v>51.08885293321879</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.861624966170384</v>
+        <v>0.3966337566213</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>4.730183966865719</v>
+        <v>-6.380307698989867</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8162</v>
+        <v>8081</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>691.4380964080913</v>
+        <v>695.8836098282997</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>82.59999999999999</v>
+        <v>318</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>64.50152834357993</v>
+        <v>62.92047720186238</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>41.71867962006188</v>
+        <v>30.62459569811681</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.687141209142974</v>
+        <v>1.861624966170384</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.6000819069730863</v>
+        <v>4.730183966865719</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8473</v>
+        <v>8162</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>689.5814624781327</v>
+        <v>691.4380964080913</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>50.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>59.99794023164745</v>
+        <v>64.50152834357993</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>34.1383393842229</v>
+        <v>41.71867962006188</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.3005834155099229</v>
+        <v>1.687141209142974</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.7147632144482721</v>
+        <v>0.6000819069730863</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8481</v>
+        <v>8473</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>681.0650869378728</v>
+        <v>689.5814624781327</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>42.1</v>
+        <v>50.8</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>64.54867046426301</v>
+        <v>59.99794023164745</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>28.61258365908864</v>
+        <v>34.1383393842229</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.568177969131644</v>
+        <v>0.3005834155099229</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.1092860738915924</v>
+        <v>-0.7147632144482721</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8358</v>
+        <v>8481</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>679.1057632678868</v>
+        <v>681.0650869378728</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>657</v>
+        <v>42.1</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>61.50723182491143</v>
+        <v>64.54867046426301</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>24.75946311702135</v>
+        <v>28.61258365908864</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.863621559834572</v>
+        <v>0.568177969131644</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2.213057556026499</v>
+        <v>0.1092860738915924</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>9930</v>
+        <v>8358</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>678.6791362515934</v>
+        <v>679.1057632678868</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>70.09999999999999</v>
+        <v>657</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>58.84031336378653</v>
+        <v>61.50723182491143</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>11.21844588706947</v>
+        <v>24.75946311702135</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.932249135801524</v>
+        <v>1.863621559834572</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.1325573082611716</v>
+        <v>2.213057556026499</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8341</v>
+        <v>9930</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>673.087333471714</v>
+        <v>678.6791362515934</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>79.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>56.6547039151308</v>
+        <v>58.84031336378653</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>26.68957542145884</v>
+        <v>11.21844588706947</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.8590362712968133</v>
+        <v>2.932249135801524</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.07566640600827521</v>
+        <v>0.1325573082611716</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8215</v>
+        <v>8341</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>665.8825256705372</v>
+        <v>673.087333471714</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>30</v>
+        <v>79.3</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>52.19334585523595</v>
+        <v>56.6547039151308</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>28.01863083463742</v>
+        <v>26.68957542145884</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.4913558385413805</v>
+        <v>0.8590362712968133</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.0039013290933949</v>
+        <v>-0.07566640600827521</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8049</v>
+        <v>8215</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>660.2605559869041</v>
+        <v>665.8825256705372</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>27.3</v>
+        <v>30</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>55.2231870434814</v>
+        <v>52.19334585523595</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>25.87632172149108</v>
+        <v>28.01863083463742</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.7137867423677872</v>
+        <v>0.4913558385413805</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.040576107839498</v>
+        <v>-0.0039013290933949</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8097</v>
+        <v>8049</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>658.3007231672585</v>
+        <v>660.2605559869041</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>60.8</v>
+        <v>27.3</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>63.03241610917366</v>
+        <v>55.2231870434814</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>26.48567015739554</v>
+        <v>25.87632172149108</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.845153455738113</v>
+        <v>0.7137867423677872</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.0601396718254807</v>
+        <v>0.040576107839498</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8088</v>
+        <v>8097</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>657.1374604960097</v>
+        <v>658.3007231672585</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>68.2</v>
+        <v>60.8</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>63.52112465827569</v>
+        <v>63.03241610917366</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>27.04796478100105</v>
+        <v>26.48567015739554</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.9891587938971432</v>
+        <v>1.845153455738113</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.5492876844673482</v>
+        <v>0.0601396718254807</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8996</v>
+        <v>8088</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>653.1475687139243</v>
+        <v>657.1374604960097</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1450</v>
+        <v>68.2</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>61.35451329465793</v>
+        <v>63.52112465827569</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>23.23288113062859</v>
+        <v>27.04796478100105</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.8637331837377973</v>
+        <v>0.9891587938971432</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>36.40534814657968</v>
+        <v>0.5492876844673482</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1905,21 +1905,21 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8086</v>
+        <v>8996</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>642.5723024899361</v>
+        <v>653.1475687139243</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>159.5</v>
+        <v>1450</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>52.06799751298394</v>
+        <v>61.35451329465793</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>22.03858852879184</v>
+        <v>23.23288113062859</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.7340044776158087</v>
+        <v>0.8637331837377973</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.3027809379918236</v>
+        <v>36.40534814657968</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8131</v>
+        <v>8086</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>638.2422447624508</v>
+        <v>642.5723024899361</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>74.8</v>
+        <v>159.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>56.24620870834666</v>
+        <v>52.06799751298394</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>16.75919661421779</v>
+        <v>22.03858852879184</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.046766458917964</v>
+        <v>0.7340044776158087</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.4724891790448904</v>
+        <v>0.3027809379918236</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8476</v>
+        <v>8131</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>604.221073373549</v>
+        <v>638.2422447624508</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>23</v>
+        <v>74.8</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>87.1930551746633</v>
+        <v>56.24620870834666</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>50.35756467404717</v>
+        <v>16.75919661421779</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.522107337354891</v>
+        <v>1.046766458917964</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.6526331269678562</v>
+        <v>0.4724891790448904</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8064</v>
+        <v>8476</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>601.6304493063188</v>
+        <v>604.221073373549</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>156</v>
+        <v>23</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,49 +2089,49 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>58.1153599412154</v>
+        <v>87.1930551746633</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>35.77723999994588</v>
+        <v>50.35756467404717</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.6364023373390481</v>
+        <v>1.522107337354891</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.8651373834170784</v>
+        <v>0.6526331269678562</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8109</v>
+        <v>8064</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>600.9608635298158</v>
+        <v>601.6304493063188</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>122.5</v>
+        <v>156</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,49 +2142,49 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>53.15277426971735</v>
+        <v>58.1153599412154</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>26.12788102677064</v>
+        <v>35.77723999994588</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.7668171020041588</v>
+        <v>0.6364023373390481</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.1831196074033463</v>
+        <v>-0.8651373834170784</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8048</v>
+        <v>8109</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>593.5930720363822</v>
+        <v>600.9608635298158</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>65.59999999999999</v>
+        <v>122.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>54.30024093540138</v>
+        <v>53.15277426971735</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>20.24212335358077</v>
+        <v>26.12788102677064</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.6747232643553024</v>
+        <v>0.7668171020041588</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.2596126075090661</v>
+        <v>0.1831196074033463</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2223,21 +2223,21 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8289</v>
+        <v>8048</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>587.5764582299207</v>
+        <v>593.5930720363822</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>61.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>45.4298641966304</v>
+        <v>54.30024093540138</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>28.53039572916956</v>
+        <v>20.24212335358077</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.5484347606570178</v>
+        <v>0.6747232643553024</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-1.505506804186731</v>
+        <v>0.2596126075090661</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8072</v>
+        <v>8289</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>586.6274616619229</v>
+        <v>587.5764582299207</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>30.6</v>
+        <v>61.2</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>61.04204257114255</v>
+        <v>45.4298641966304</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>24.97160368031004</v>
+        <v>28.53039572916956</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.571701232284628</v>
+        <v>0.5484347606570178</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.1960233551349544</v>
+        <v>-1.505506804186731</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8150</v>
+        <v>8072</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>581.7141033183194</v>
+        <v>586.6274616619229</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>106.5</v>
+        <v>30.6</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>58.94078913703267</v>
+        <v>61.04204257114255</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>28.76074721054344</v>
+        <v>24.97160368031004</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.423286842132141</v>
+        <v>1.571701232284628</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.672117088558025</v>
+        <v>0.1960233551349544</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8182</v>
+        <v>8150</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>573.5489904516652</v>
+        <v>581.7141033183194</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>47.3</v>
+        <v>106.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>51.46084087654371</v>
+        <v>58.94078913703267</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>26.38324987694136</v>
+        <v>28.76074721054344</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.3227681935608106</v>
+        <v>1.423286842132141</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.4872326438279124</v>
+        <v>0.672117088558025</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8110</v>
+        <v>8182</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>571.5660725772533</v>
+        <v>573.5489904516652</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>58.5</v>
+        <v>47.3</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>54.21946479930008</v>
+        <v>51.46084087654371</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>19.92856071642719</v>
+        <v>26.38324987694136</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.5872627471217886</v>
+        <v>0.3227681935608106</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.1594941621079859</v>
+        <v>-0.4872326438279124</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>9105</v>
+        <v>8110</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>566.4384600422302</v>
+        <v>571.5660725772533</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>9.130000000000001</v>
+        <v>58.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>52.32808943767304</v>
+        <v>54.21946479930008</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>44.18312856046992</v>
+        <v>19.92856071642719</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.5187642198471959</v>
+        <v>0.5872627471217886</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.2280971419995638</v>
+        <v>0.1594941621079859</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8390</v>
+        <v>9105</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>557.7791923897609</v>
+        <v>566.4384600422302</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>113.5</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>48.70926219499025</v>
+        <v>52.32808943767304</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>24.5115725942286</v>
+        <v>44.18312856046992</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.4558294821465532</v>
+        <v>0.5187642198471959</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-1.598875043135461</v>
+        <v>-0.2280971419995638</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>9103</v>
+        <v>8390</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>544.1504451692974</v>
+        <v>557.7791923897609</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>5.34</v>
+        <v>113.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>48.98189214010333</v>
+        <v>48.70926219499025</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>29.49259628682477</v>
+        <v>24.5115725942286</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.2916929664188186</v>
+        <v>0.4558294821465532</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.07060985961553209</v>
+        <v>-1.598875043135461</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8488</v>
+        <v>9103</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>521.5635722013346</v>
+        <v>544.1504451692974</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>10.4</v>
+        <v>5.34</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>53.1878802357208</v>
+        <v>48.98189214010333</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>11.96697836464333</v>
+        <v>29.49259628682477</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.3568717452351924</v>
+        <v>0.2916929664188186</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0272850078908807</v>
+        <v>-0.07060985961553209</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8210</v>
+        <v>8488</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>510.0525224308171</v>
+        <v>521.5635722013346</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>1310</v>
+        <v>10.4</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>45.02415466285611</v>
+        <v>53.1878802357208</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>19.25192023133519</v>
+        <v>11.96697836464333</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.7979103480515545</v>
+        <v>0.3568717452351924</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-20.53181534426995</v>
+        <v>0.0272850078908807</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8499</v>
+        <v>8210</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>506.2965534246763</v>
+        <v>510.0525224308171</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>312</v>
+        <v>1310</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>56.59367229416853</v>
+        <v>45.02415466285611</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>16.94162368864549</v>
+        <v>19.25192023133519</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.426404703933311</v>
+        <v>0.7979103480515545</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>2.131196163206268</v>
+        <v>-20.53181534426995</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8104</v>
+        <v>8499</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>504.2243598864613</v>
+        <v>506.2965534246763</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>40.1</v>
+        <v>312</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>52.85702538411136</v>
+        <v>56.59367229416853</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>31.06717266583345</v>
+        <v>16.94162368864549</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.4692124351729209</v>
+        <v>1.426404703933311</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.1024493115654798</v>
+        <v>2.131196163206268</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>9908</v>
+        <v>8104</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>大台北</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>502.2649354422237</v>
+        <v>504.2243598864613</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>29.8</v>
+        <v>40.1</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>62.60910402389672</v>
+        <v>52.85702538411136</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>17.32423348662813</v>
+        <v>31.06717266583345</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.300261649462139</v>
+        <v>0.4692124351729209</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.0525492200518207</v>
+        <v>-0.1024493115654798</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>9905</v>
+        <v>9908</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>大台北</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>498.9580330548551</v>
+        <v>502.2649354422237</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>21</v>
+        <v>29.8</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>55.46267573307806</v>
+        <v>62.60910402389672</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>17.14107795831815</v>
+        <v>17.32423348662813</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5937281479778218</v>
+        <v>1.300261649462139</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0556871511838923</v>
+        <v>0.0525492200518207</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8472</v>
+        <v>9905</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>495.0880752496048</v>
+        <v>498.9580330548551</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>83.90000000000001</v>
+        <v>21</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>52.83183399978737</v>
+        <v>55.46267573307806</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>24.81574586370139</v>
+        <v>17.14107795831815</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.0352362665995166</v>
+        <v>0.5937281479778218</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.917500762794706</v>
+        <v>0.0556871511838923</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8299</v>
+        <v>8472</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>491.3749957309319</v>
+        <v>495.0880752496048</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>2430</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,49 +3043,49 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>51.23782465791624</v>
+        <v>52.83183399978737</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>14.74160768490879</v>
+        <v>24.81574586370139</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.918560273667126</v>
+        <v>0.0352362665995166</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-5.975932897375053</v>
+        <v>-0.917500762794706</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8050</v>
+        <v>8299</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>490.2432069677416</v>
+        <v>491.3749957309319</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>55.4</v>
+        <v>2430</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,49 +3096,49 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>52.40667292685251</v>
+        <v>51.23782465791624</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>40.92912180108031</v>
+        <v>14.74160768490879</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.2289730639942828</v>
+        <v>0.918560273667126</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.7425687125967033</v>
+        <v>-5.975932897375053</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8102</v>
+        <v>8050</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>489.5740438792059</v>
+        <v>490.2432069677416</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>71</v>
+        <v>55.4</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>51.44137720246125</v>
+        <v>52.40667292685251</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>10.35422832561212</v>
+        <v>40.92912180108031</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.1749299082217056</v>
+        <v>0.2289730639942828</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.6842958785203521</v>
+        <v>-0.7425687125967033</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8155</v>
+        <v>8102</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>481.2190253820245</v>
+        <v>489.5740438792059</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>388.5</v>
+        <v>71</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>50.29052502296679</v>
+        <v>51.44137720246125</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>17.5164289740673</v>
+        <v>10.35422832561212</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.8524233311987289</v>
+        <v>0.1749299082217056</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>2.492078303165823</v>
+        <v>-0.6842958785203521</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8383</v>
+        <v>8155</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>478.0104108183502</v>
+        <v>481.2190253820245</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>59.6</v>
+        <v>388.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>50.38583226721376</v>
+        <v>50.29052502296679</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>16.07128253167966</v>
+        <v>17.5164289740673</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.8002759405496944</v>
+        <v>0.8524233311987289</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.028058394726162</v>
+        <v>2.492078303165823</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8240</v>
+        <v>8383</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>475.8282358189402</v>
+        <v>478.0104108183502</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>57</v>
+        <v>59.6</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>43.38377925235798</v>
+        <v>50.38583226721376</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>15.82236503442872</v>
+        <v>16.07128253167966</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.045439760394191</v>
+        <v>0.8002759405496944</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0341471408971212</v>
+        <v>0.028058394726162</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8069</v>
+        <v>8240</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>473.9580987944599</v>
+        <v>475.8282358189402</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>196</v>
+        <v>57</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>46.466466041289</v>
+        <v>43.38377925235798</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>22.13040105424878</v>
+        <v>15.82236503442872</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.5658165938389305</v>
+        <v>1.045439760394191</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-2.927727830187713</v>
+        <v>0.0341471408971212</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>9906</v>
+        <v>8069</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>欣巴巴</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>471.6189729812961</v>
+        <v>473.9580987944599</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>42.7</v>
+        <v>196</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>54.61806101889957</v>
+        <v>46.466466041289</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>41.94600877907362</v>
+        <v>22.13040105424878</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.3919201778112747</v>
+        <v>0.5658165938389305</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.2525468822646839</v>
+        <v>-2.927727830187713</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8084</v>
+        <v>9906</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>欣巴巴</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>468.9228313456316</v>
+        <v>471.6189729812961</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>50</v>
+        <v>42.7</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>61.21492406935504</v>
+        <v>54.61806101889957</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>19.27118647884373</v>
+        <v>41.94600877907362</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.499374785742561</v>
+        <v>0.3919201778112747</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.2070595000885087</v>
+        <v>0.2525468822646839</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8277</v>
+        <v>8084</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>465.4577943302612</v>
+        <v>468.9228313456316</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>10.85</v>
+        <v>50</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>61.6223444916603</v>
+        <v>61.21492406935504</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>30.91084856788684</v>
+        <v>19.27118647884373</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.9926647899829484</v>
+        <v>1.499374785742561</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.0595330544507243</v>
+        <v>0.2070595000885087</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>9912</v>
+        <v>8277</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>462.5254779946099</v>
+        <v>465.4577943302612</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>12.6</v>
+        <v>10.85</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>53.6843486887205</v>
+        <v>61.6223444916603</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>23.24210201748755</v>
+        <v>30.91084856788684</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.1637310654190126</v>
+        <v>0.9926647899829484</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0075562706145754</v>
+        <v>-0.0595330544507243</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8087</v>
+        <v>9912</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>441.4074154197762</v>
+        <v>462.5254779946099</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>32.9</v>
+        <v>12.6</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>43.31558781255821</v>
+        <v>53.6843486887205</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>18.25435968540868</v>
+        <v>23.24210201748755</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.4143079321973802</v>
+        <v>0.1637310654190126</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.2885733913564145</v>
+        <v>0.0075562706145754</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8422</v>
+        <v>8087</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>423.4366597815709</v>
+        <v>441.4074154197762</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>29</v>
+        <v>32.9</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>55.16474928775377</v>
+        <v>43.31558781255821</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>16.45022101854169</v>
+        <v>18.25435968540868</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.5568646625253085</v>
+        <v>0.4143079321973802</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0751846492919611</v>
+        <v>-0.2885733913564145</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8093</v>
+        <v>8422</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>419.4542699271906</v>
+        <v>423.4366597815709</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>18.85</v>
+        <v>29</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>51.76021267462438</v>
+        <v>55.16474928775377</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>8.145455728452427</v>
+        <v>16.45022101854169</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.0853663416521054</v>
+        <v>0.5568646625253085</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.3993342808243402</v>
+        <v>0.0751846492919611</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8227</v>
+        <v>8093</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>414.3347197423665</v>
+        <v>419.4542699271906</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>186.5</v>
+        <v>18.85</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>47.55252056227626</v>
+        <v>51.76021267462438</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>21.41072467619774</v>
+        <v>8.145455728452427</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.5654184599986261</v>
+        <v>0.0853663416521054</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-2.168460102758188</v>
+        <v>0.3993342808243402</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8271</v>
+        <v>8227</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>407.0635221739278</v>
+        <v>414.3347197423665</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>205.5</v>
+        <v>186.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>43.28342104981526</v>
+        <v>47.55252056227626</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>18.94527173738791</v>
+        <v>21.41072467619774</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.6156420877115504</v>
+        <v>0.5654184599986261</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-2.119522498787211</v>
+        <v>-2.168460102758188</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8074</v>
+        <v>8271</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>404.474185406169</v>
+        <v>407.0635221739278</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>73</v>
+        <v>205.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>47.98237038981743</v>
+        <v>43.28342104981526</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>11.54521426701848</v>
+        <v>18.94527173738791</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.027068753224825</v>
+        <v>0.6156420877115504</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.2310997711313505</v>
+        <v>-2.119522498787211</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8455</v>
+        <v>8074</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>402.6780796579882</v>
+        <v>404.474185406169</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>39.21024793481621</v>
+        <v>47.98237038981743</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>21.11941127743839</v>
+        <v>11.54521426701848</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.142854834735613</v>
+        <v>1.027068753224825</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-1.020569580188748</v>
+        <v>0.2310997711313505</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8068</v>
+        <v>8455</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>391.9390224176289</v>
+        <v>402.6780796579882</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>19.35</v>
+        <v>28</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>44.30963096320023</v>
+        <v>39.21024793481621</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>21.07429304766227</v>
+        <v>21.11941127743839</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.917541205688285</v>
+        <v>1.142854834735613</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.1348633659402012</v>
+        <v>-1.020569580188748</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>9911</v>
+        <v>8068</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>371.8001224994576</v>
+        <v>391.9390224176289</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>82.59999999999999</v>
+        <v>19.35</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>43.63436464857219</v>
+        <v>44.30963096320023</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15.09442260063078</v>
+        <v>21.07429304766227</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.6806265468537439</v>
+        <v>0.917541205688285</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.1361800737124519</v>
+        <v>0.1348633659402012</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>9910</v>
+        <v>9911</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>櫻花</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>371.0067443841326</v>
+        <v>371.8001224994576</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>42.9086432251033</v>
+        <v>43.63436464857219</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>23.48978513601457</v>
+        <v>15.09442260063078</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.3160802773237927</v>
+        <v>0.6806265468537439</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-1.56053850739707</v>
+        <v>-0.1361800737124519</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8067</v>
+        <v>9910</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>362.1247911744752</v>
+        <v>371.0067443841326</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>13</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>51.38699410105697</v>
+        <v>42.9086432251033</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>6.292660065458068</v>
+        <v>23.48978513601457</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.9209847810710292</v>
+        <v>0.3160802773237927</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.1239959068500193</v>
+        <v>-1.56053850739707</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8089</v>
+        <v>8067</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>352.3103951005759</v>
+        <v>362.1247911744752</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>20.4</v>
+        <v>13</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>46.61600769605353</v>
+        <v>51.38699410105697</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>34.76108163047293</v>
+        <v>6.292660065458068</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.4262400846063936</v>
+        <v>0.9209847810710292</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.017412579432692</v>
+        <v>-0.1239959068500193</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8103</v>
+        <v>8089</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>339.5731876248861</v>
+        <v>352.3103951005759</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>97.40000000000001</v>
+        <v>20.4</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>44.70691195735639</v>
+        <v>46.61600769605353</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>21.13206731413157</v>
+        <v>34.76108163047293</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.550296101209379</v>
+        <v>0.4262400846063936</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.2162075660894791</v>
+        <v>0.017412579432692</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8442</v>
+        <v>8103</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>336.8448476053441</v>
+        <v>339.5731876248861</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>40.55</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>40.82635727905032</v>
+        <v>44.70691195735639</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>21.89827073855919</v>
+        <v>21.13206731413157</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.286429133050732</v>
+        <v>0.550296101209379</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.4614607433019853</v>
+        <v>-0.2162075660894791</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8101</v>
+        <v>8442</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>312.6832282941425</v>
+        <v>336.8448476053441</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>13.75</v>
+        <v>40.55</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>44.82269502083291</v>
+        <v>40.82635727905032</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>15.07404812772795</v>
+        <v>21.89827073855919</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5016509648299052</v>
+        <v>1.286429133050732</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.2496876310379848</v>
+        <v>0.4614607433019853</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8183</v>
+        <v>8101</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>312.5978753445236</v>
+        <v>312.6832282941425</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>32.35</v>
+        <v>13.75</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>50.10453812044537</v>
+        <v>44.82269502083291</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>13.8786578511923</v>
+        <v>15.07404812772795</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.9480619811913542</v>
+        <v>0.5016509648299052</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.1694359308368792</v>
+        <v>-0.2496876310379848</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8114</v>
+        <v>8183</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>308.4219018000724</v>
+        <v>312.5978753445236</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>207</v>
+        <v>32.35</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>43.12814158196543</v>
+        <v>50.10453812044537</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>25.59970891501981</v>
+        <v>13.8786578511923</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.7634395058788715</v>
+        <v>0.9480619811913542</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-3.221063714234528</v>
+        <v>0.1694359308368792</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8176</v>
+        <v>8114</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>305.3534311045403</v>
+        <v>308.4219018000724</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>10.05</v>
+        <v>207</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>43.65054714179532</v>
+        <v>43.12814158196543</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>8.666807810402311</v>
+        <v>25.59970891501981</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.029462806985472</v>
+        <v>0.7634395058788715</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0008604268700389</v>
+        <v>-3.221063714234528</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8443</v>
+        <v>8176</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>303.4867316979008</v>
+        <v>305.3534311045403</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>11.5</v>
+        <v>10.05</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>54.91762868774698</v>
+        <v>43.65054714179532</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>53.68040583264136</v>
+        <v>8.666807810402311</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.4122407991966426</v>
+        <v>1.029462806985472</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0322383629309855</v>
+        <v>-0.0008604268700389</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8477</v>
+        <v>8443</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>297.2594229051118</v>
+        <v>303.4867316979008</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>54.7508236945582</v>
+        <v>54.91762868774698</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>27.57319818770709</v>
+        <v>53.68040583264136</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.2826355581075908</v>
+        <v>0.4122407991966426</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.2420889009841552</v>
+        <v>0.0322383629309855</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8147</v>
+        <v>8477</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>295.3099876453169</v>
+        <v>297.2594229051118</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>145</v>
+        <v>18</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>39.67552687874783</v>
+        <v>54.7508236945582</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>20.90596753450369</v>
+        <v>27.57319818770709</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.3177473756476709</v>
+        <v>0.2826355581075908</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-1.220855469253969</v>
+        <v>-0.2420889009841552</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>9110</v>
+        <v>8147</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>281.8180061690114</v>
+        <v>295.3099876453169</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>15.99527001672097</v>
+        <v>39.67552687874783</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>18.64180333268789</v>
+        <v>20.90596753450369</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0</v>
+        <v>0.3177473756476709</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.2527515507927629</v>
+        <v>-1.220855469253969</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>9907</v>
+        <v>9110</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>統一實</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>278.4210389788527</v>
+        <v>281.8180061690114</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>15.15</v>
+        <v>0</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>24.71514578221152</v>
+        <v>15.99527001672097</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>25.15629359276496</v>
+        <v>18.64180333268789</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.428851905686855</v>
+        <v>0</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.0799440682157733</v>
+        <v>-0.2527515507927629</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8411</v>
+        <v>9907</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>統一實</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>270.5354675612544</v>
+        <v>278.4210389788527</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>11.95</v>
+        <v>15.15</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>42.74419322922319</v>
+        <v>24.71514578221152</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>35.29472906786312</v>
+        <v>25.15629359276496</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4767384702607667</v>
+        <v>1.428851905686855</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0102356555491902</v>
+        <v>-0.0799440682157733</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8111</v>
+        <v>8411</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>265.7501952435061</v>
+        <v>270.5354675612544</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>55.3</v>
+        <v>11.95</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>36.36266567913383</v>
+        <v>42.74419322922319</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>27.75492923407554</v>
+        <v>35.29472906786312</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.7796426718430025</v>
+        <v>0.4767384702607667</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.2560925472107631</v>
+        <v>-0.0102356555491902</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8464</v>
+        <v>8111</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>265.7126636425585</v>
+        <v>265.7501952435061</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>343.5</v>
+        <v>55.3</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>54.09381927077531</v>
+        <v>36.36266567913383</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>17.38405019161562</v>
+        <v>27.75492923407554</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.246458487941021</v>
+        <v>0.7796426718430025</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>2.661152228337976</v>
+        <v>-0.2560925472107631</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8482</v>
+        <v>8464</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>265.5745615466516</v>
+        <v>265.7126636425585</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>49.4</v>
+        <v>343.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>52.03121982999596</v>
+        <v>54.09381927077531</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>7.427784102563045</v>
+        <v>17.38405019161562</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5575999274902566</v>
+        <v>1.246458487941021</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.1801743487657041</v>
+        <v>2.661152228337976</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8429</v>
+        <v>8482</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>263.6169617594323</v>
+        <v>265.5745615466516</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>6.35</v>
+        <v>49.4</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>42.43652851501123</v>
+        <v>52.03121982999596</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>23.35004642945175</v>
+        <v>7.427784102563045</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.536643677609937</v>
+        <v>0.5575999274902566</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.015934773061375</v>
+        <v>-0.1801743487657041</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8463</v>
+        <v>8429</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>263.3224160088297</v>
+        <v>263.6169617594323</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>21.35</v>
+        <v>6.35</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>39.44939151292404</v>
+        <v>42.43652851501123</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>13.98230731607946</v>
+        <v>23.35004642945175</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.824315656721316</v>
+        <v>0.536643677609937</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0439282126064131</v>
+        <v>-0.015934773061375</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8213</v>
+        <v>8463</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>258.4046715807425</v>
+        <v>263.3224160088297</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>37.05</v>
+        <v>21.35</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>49.83611476894181</v>
+        <v>39.44939151292404</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>13.73700953646125</v>
+        <v>13.98230731607946</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.6540539254263622</v>
+        <v>1.824315656721316</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0354976444167235</v>
+        <v>-0.0439282126064131</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8932</v>
+        <v>8213</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>253.4294427963872</v>
+        <v>258.4046715807425</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>100.5</v>
+        <v>37.05</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>50.97521094592191</v>
+        <v>49.83611476894181</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>14.06620505469196</v>
+        <v>13.73700953646125</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.6137899975030047</v>
+        <v>0.6540539254263622</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.319567379743042</v>
+        <v>0.0354976444167235</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>9904</v>
+        <v>8932</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>251.5939451487517</v>
+        <v>253.4294427963872</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>26</v>
+        <v>100.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>45.87053755522876</v>
+        <v>50.97521094592191</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>15.63412567950932</v>
+        <v>14.06620505469196</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.9829829207334204</v>
+        <v>0.6137899975030047</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0096577501752237</v>
+        <v>-0.319567379743042</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8374</v>
+        <v>9904</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>250.8012351714846</v>
+        <v>251.5939451487517</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>90.40000000000001</v>
+        <v>26</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>45.23846086260021</v>
+        <v>45.87053755522876</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>17.06047327317276</v>
+        <v>15.63412567950932</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.2723314549481139</v>
+        <v>0.9829829207334204</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-1.136218647135577</v>
+        <v>0.0096577501752237</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8478</v>
+        <v>8374</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>241.7241681571049</v>
+        <v>250.8012351714846</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>152</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>43.45666223546137</v>
+        <v>45.23846086260021</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>15.18050058673783</v>
+        <v>17.06047327317276</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.3431269125502306</v>
+        <v>0.2723314549481139</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.2386224838832471</v>
+        <v>-1.136218647135577</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8201</v>
+        <v>8478</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>241.5542647673434</v>
+        <v>241.7241681571049</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>13.05</v>
+        <v>152</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>46.34959719865276</v>
+        <v>43.45666223546137</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>21.48612703161893</v>
+        <v>15.18050058673783</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.4515606044512028</v>
+        <v>0.3431269125502306</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.041975795307972</v>
+        <v>-0.2386224838832471</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8487</v>
+        <v>8201</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>230.6031056584428</v>
+        <v>241.5542647673434</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>78.8</v>
+        <v>13.05</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>46.49962470301764</v>
+        <v>46.34959719865276</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>15.36168040088902</v>
+        <v>21.48612703161893</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.63241115645091</v>
+        <v>0.4515606044512028</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.26719054734469</v>
+        <v>-0.041975795307972</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8423</v>
+        <v>8487</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>226.6535213779775</v>
+        <v>230.6031056584428</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>17.8</v>
+        <v>78.8</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>49.26557208232486</v>
+        <v>46.49962470301764</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>12.08905192142642</v>
+        <v>15.36168040088902</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.369124521285513</v>
+        <v>0.63241115645091</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.0133296368171201</v>
+        <v>-0.26719054734469</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8462</v>
+        <v>8423</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>221.3459551832071</v>
+        <v>226.6535213779775</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>138.5</v>
+        <v>17.8</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>43.55459282630165</v>
+        <v>49.26557208232486</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>17.49799163081332</v>
+        <v>12.08905192142642</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.8241728766516228</v>
+        <v>0.369124521285513</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.305039186755669</v>
+        <v>0.0133296368171201</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8367</v>
+        <v>8462</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>218.7790692646309</v>
+        <v>221.3459551832071</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>40.45</v>
+        <v>138.5</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>40.10630767712123</v>
+        <v>43.55459282630165</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>23.43615286050267</v>
+        <v>17.49799163081332</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.8391522150392297</v>
+        <v>0.8241728766516228</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.07530525293116599</v>
+        <v>-0.305039186755669</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8249</v>
+        <v>8367</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>206.6206919293584</v>
+        <v>218.7790692646309</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>51.4</v>
+        <v>40.45</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>47.30198128814829</v>
+        <v>40.10630767712123</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>17.12987036386708</v>
+        <v>23.43615286050267</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.3256837442043904</v>
+        <v>0.8391522150392297</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.1974388331675615</v>
+        <v>0.07530525293116599</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8080</v>
+        <v>8249</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>201.8355642671046</v>
+        <v>206.6206919293584</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>27.9</v>
+        <v>51.4</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>47.23998423092257</v>
+        <v>47.30198128814829</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>46.38429987890565</v>
+        <v>17.12987036386708</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.941399676689857</v>
+        <v>0.3256837442043904</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0265559124224529</v>
+        <v>-0.1974388331675615</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8940</v>
+        <v>8080</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>183.3980259817191</v>
+        <v>201.8355642671046</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>16.65</v>
+        <v>27.9</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>46.07017572683471</v>
+        <v>47.23998423092257</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>14.8776851060167</v>
+        <v>46.38429987890565</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.8298596579497132</v>
+        <v>0.941399676689857</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0571763391675099</v>
+        <v>0.0265559124224529</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>9955</v>
+        <v>8940</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>178.6393817524421</v>
+        <v>183.3980259817191</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>26.85</v>
+        <v>16.65</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>41.21029036166458</v>
+        <v>46.07017572683471</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>22.10648536135053</v>
+        <v>14.8776851060167</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6131050925427566</v>
+        <v>0.8298596579497132</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0115354112286019</v>
+        <v>0.0571763391675099</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8410</v>
+        <v>9955</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>178.4638398921316</v>
+        <v>178.6393817524421</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>32.35</v>
+        <v>26.85</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>32.68950704135716</v>
+        <v>41.21029036166458</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>22.4736805221894</v>
+        <v>22.10648536135053</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.246383989213159</v>
+        <v>0.6131050925427566</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.1320816510866104</v>
+        <v>0.0115354112286019</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5933,21 +5933,21 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8222</v>
+        <v>8410</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>171.572241877613</v>
+        <v>178.4638398921316</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>35.5</v>
+        <v>32.35</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>48.78576827480225</v>
+        <v>32.68950704135716</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>13.53555748221636</v>
+        <v>22.4736805221894</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.766942169496679</v>
+        <v>1.246383989213159</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.051373907970501</v>
+        <v>-0.1320816510866104</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8431</v>
+        <v>8222</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>166.4997938876605</v>
+        <v>171.572241877613</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>55</v>
+        <v>35.5</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>48.51820166689556</v>
+        <v>48.78576827480225</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>16.20818606031471</v>
+        <v>13.53555748221636</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.5230197345834665</v>
+        <v>0.766942169496679</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.8803302436896623</v>
+        <v>0.051373907970501</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8059</v>
+        <v>8431</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>163.9956441620097</v>
+        <v>166.4997938876605</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>16.9</v>
+        <v>55</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>33.70775268838996</v>
+        <v>48.51820166689556</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>17.3022161620801</v>
+        <v>16.20818606031471</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.548270641022742</v>
+        <v>0.5230197345834665</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.2062692820732866</v>
+        <v>0.8803302436896623</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, dealer_buy_3d</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8085</v>
+        <v>8059</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>160.9294398573599</v>
+        <v>163.9956441620097</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>12.25</v>
+        <v>16.9</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>44.51654755585871</v>
+        <v>33.70775268838996</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>20.08022880616156</v>
+        <v>17.3022161620801</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.8700243819914563</v>
+        <v>0.548270641022742</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0631018615093616</v>
+        <v>-0.2062692820732866</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8440</v>
+        <v>8085</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>157.8225104383756</v>
+        <v>160.9294398573599</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>21.8</v>
+        <v>12.25</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>42.7360636634348</v>
+        <v>44.51654755585871</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>12.41521496946988</v>
+        <v>20.08022880616156</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3724603374130559</v>
+        <v>0.8700243819914563</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.1325498584806576</v>
+        <v>-0.0631018615093616</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8092</v>
+        <v>8440</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>154.6645241811281</v>
+        <v>157.8225104383756</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>14.1</v>
+        <v>21.8</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>31.39429074483249</v>
+        <v>42.7360636634348</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>18.27966154853917</v>
+        <v>12.41521496946988</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.6344482455999652</v>
+        <v>0.3724603374130559</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.2190501798120991</v>
+        <v>-0.1325498584806576</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8234</v>
+        <v>8092</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>149.9703243980113</v>
+        <v>154.6645241811281</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>64.3</v>
+        <v>14.1</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>45.15086646175843</v>
+        <v>31.39429074483249</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>17.05240239564467</v>
+        <v>18.27966154853917</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.55060053433783</v>
+        <v>0.6344482455999652</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.3871666432378859</v>
+        <v>-0.2190501798120991</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>9902</v>
+        <v>8234</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>147.7554039985121</v>
+        <v>149.9703243980113</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>13.6</v>
+        <v>64.3</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>42.17455023650646</v>
+        <v>45.15086646175843</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>14.12230044202125</v>
+        <v>17.05240239564467</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.073658647596305</v>
+        <v>0.55060053433783</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0001216184892246</v>
+        <v>-0.3871666432378859</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8466</v>
+        <v>9902</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>141.8325487308763</v>
+        <v>147.7554039985121</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>15.6</v>
+        <v>13.6</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>46.57420924828515</v>
+        <v>42.17455023650646</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>19.46398418278059</v>
+        <v>14.12230044202125</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.198432488371461</v>
+        <v>1.073658647596305</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0104414380961902</v>
+        <v>0.0001216184892246</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8404</v>
+        <v>8466</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>134.2427544305237</v>
+        <v>141.8325487308763</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>44.12771894535064</v>
+        <v>46.57420924828515</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>13.26263831555288</v>
+        <v>19.46398418278059</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.6465518573085458</v>
+        <v>0.198432488371461</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0373622073233545</v>
+        <v>-0.0104414380961902</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>9802</v>
+        <v>8404</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>128.2083852854139</v>
+        <v>134.2427544305237</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>16.7</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>39.39658208387237</v>
+        <v>44.12771894535064</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>13.69876815713244</v>
+        <v>13.26263831555288</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.3982581294123505</v>
+        <v>0.6465518573085458</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.3658597103436258</v>
+        <v>-0.0373622073233545</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>8171</v>
+        <v>9802</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>108.6276292887747</v>
+        <v>128.2083852854139</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>21.45</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>40.69183114369692</v>
+        <v>39.39658208387237</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>18.2830854961379</v>
+        <v>13.69876815713244</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.5894531429303892</v>
+        <v>0.3982581294123505</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,62 +6559,115 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.2226680841593348</v>
+        <v>-0.3658597103436258</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
+        <v>8171</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>天宇</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>108.6276292887747</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>40.69183114369692</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>18.2830854961379</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.5894531429303892</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>-0.2226680841593348</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
         <v>8467</v>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>波力-KY</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D116" s="2" t="n">
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
         <v>64.94445787847906</v>
       </c>
-      <c r="E116" s="2" t="n">
+      <c r="E117" s="2" t="n">
         <v>123.5</v>
       </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H116" s="2" t="n">
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
         <v>49.86489936557564</v>
       </c>
-      <c r="I116" s="2" t="n">
+      <c r="I117" s="2" t="n">
         <v>15.94770089903274</v>
       </c>
-      <c r="J116" s="2" t="n">
+      <c r="J117" s="2" t="n">
         <v>1.283053976653244</v>
       </c>
-      <c r="K116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N116" s="2" t="n">
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
         <v>1.844114534594008</v>
       </c>
-      <c r="O116" s="2" t="inlineStr">
+      <c r="O117" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>

--- a/output/full_scan/batch_seq0_2026-06-23.xlsx
+++ b/output/full_scan/batch_seq0_2026-06-23.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>888.6117038582964</v>
+        <v>1088.611703858297</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>124.5</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>74.77480889953168</v>
+        <v>74.7748089924718</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>14.17708843597372</v>
+        <v>14.17708843906264</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>4.961170385829647</v>
@@ -570,11 +570,11 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>2.033970382169455</v>
+        <v>2.033970381551301</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>831.1499498400875</v>
+        <v>1031.149949840087</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>101</v>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>66.49672141866306</v>
+        <v>66.49672142365438</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>17.53502627632523</v>
+        <v>17.53502625429774</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>3.561320263844479</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,11 +623,11 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>1.664644117175211</v>
+        <v>1.664644117164898</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>798.9212781920777</v>
+        <v>1018.921278192078</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>260</v>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>79.18996982791705</v>
+        <v>79.18996983816785</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>41.77081957580836</v>
+        <v>41.77081955877879</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>2.003883040149578</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>7.193435249960281</v>
+        <v>7.193435249712971</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>9136</v>
+        <v>8926</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>774.2277711892747</v>
+        <v>1006.019246629861</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>16.25</v>
+        <v>82.2</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>64.69889611732533</v>
+        <v>73.57605855891302</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>51.82967023122704</v>
+        <v>52.81843204284518</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.3646071694043747</v>
+        <v>0.90705048173175</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.2613371780321372</v>
+        <v>0.2672039609074312</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>8076</v>
+        <v>8081</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>759.2336304785372</v>
+        <v>980.8836098282997</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>25.2</v>
+        <v>318</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,49 +764,49 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>47.33341429748138</v>
+        <v>62.92047720968981</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>20.16915012029082</v>
+        <v>30.62459570195282</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.559717668581182</v>
+        <v>1.861624966170384</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.2385221230700861</v>
+        <v>4.730183966968729</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>8163</v>
+        <v>8091</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>743.8912534400679</v>
+        <v>899.442635541321</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>42.5</v>
+        <v>280.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>59.37129545789711</v>
+        <v>63.8233249697116</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>48.23176146942297</v>
+        <v>35.58371437532692</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.6098080186842006</v>
+        <v>1.903588674919304</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.1609998521336555</v>
+        <v>1.289987707026787</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8071</v>
+        <v>8162</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>740.5861011716337</v>
+        <v>851.4380964080913</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>27</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>62.00720264562619</v>
+        <v>64.5015283456984</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>44.6668774013128</v>
+        <v>41.71867963205919</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.6802828435165098</v>
+        <v>1.687141209142974</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.3826785775440759</v>
+        <v>0.6000819069730863</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8121</v>
+        <v>9136</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>733.5628632055822</v>
+        <v>849.2277711892747</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>49</v>
+        <v>16.25</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>61.96837312250334</v>
+        <v>64.69889608383177</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>47.69460317301479</v>
+        <v>51.82967024489571</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.479167186344255</v>
+        <v>0.3646071694043747</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.6304143502164665</v>
+        <v>-0.261337178054803</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8112</v>
+        <v>8499</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>729.5369302930279</v>
+        <v>831.2965534246764</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>95.8</v>
+        <v>312</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>55.71163146619102</v>
+        <v>56.59367230138228</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>26.59203057935356</v>
+        <v>16.94162369523702</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.8046109638442666</v>
+        <v>1.426404703933311</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2993059659172479</v>
+        <v>2.131196163309278</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8091</v>
+        <v>8476</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>729.442635541321</v>
+        <v>804.221073373549</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>280.5</v>
+        <v>23</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>63.8233249697116</v>
+        <v>87.1930551846994</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>35.58371439180537</v>
+        <v>50.35756465306137</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.903588674919304</v>
+        <v>1.522107337354891</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>1.289987706820714</v>
+        <v>0.6526331269472525</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8926</v>
+        <v>8105</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>721.0192466298612</v>
+        <v>798.5449428456333</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>82.2</v>
+        <v>21.4</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>73.57605853367642</v>
+        <v>59.25216099401049</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>52.81843205168666</v>
+        <v>41.71441254442549</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.90705048173175</v>
+        <v>0.6316170632091666</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.2672039609383443</v>
+        <v>-0.0383516434842576</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8070</v>
+        <v>8088</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>718.462045289231</v>
+        <v>797.1374604960096</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>58.6</v>
+        <v>68.2</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>60.81457906733305</v>
+        <v>63.52112471020022</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>28.07914488220766</v>
+        <v>27.0479649433164</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.394109889830346</v>
+        <v>0.9891587938971432</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.4432458620846322</v>
+        <v>0.5492876840861389</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8096</v>
+        <v>8358</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>714.2689524713386</v>
+        <v>794.2554221863167</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>150.5</v>
+        <v>657</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,49 +1188,49 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>65.89018543208368</v>
+        <v>61.50723182825833</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>44.45932241164056</v>
+        <v>24.75946309800149</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.8422946702833084</v>
+        <v>1.880115255360555</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>1.720895426174769</v>
+        <v>2.213057555923442</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8105</v>
+        <v>8341</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>703.5449428456333</v>
+        <v>783.087333471714</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>21.4</v>
+        <v>79.3</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>59.25216096614788</v>
+        <v>56.65470412035369</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>41.71441254442549</v>
+        <v>26.68957542145885</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.6316170632091666</v>
+        <v>0.8590362712968133</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.0383516434327406</v>
+        <v>-0.07566640621432839</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8454</v>
+        <v>8150</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>700.7486541667641</v>
+        <v>781.7141033183194</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>330</v>
+        <v>106.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>57.40891596890565</v>
+        <v>58.94078914281846</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>51.08885293321879</v>
+        <v>28.76074719455765</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.3966337566213</v>
+        <v>1.423286842132141</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-6.380307698989867</v>
+        <v>0.6721170884858951</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8081</v>
+        <v>8097</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>695.8836098282997</v>
+        <v>773.3007231672585</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>318</v>
+        <v>60.8</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>62.92047720186238</v>
+        <v>63.03241623790181</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>30.62459569811681</v>
+        <v>26.48567015739554</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.861624966170384</v>
+        <v>1.845153455738113</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>4.730183966865719</v>
+        <v>0.0601396716194335</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8162</v>
+        <v>8064</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>691.4380964080913</v>
+        <v>771.6304493063188</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>82.59999999999999</v>
+        <v>156</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,49 +1400,49 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>64.50152834357993</v>
+        <v>58.11535995748958</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>41.71867962006188</v>
+        <v>35.77723998774513</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.687141209142974</v>
+        <v>0.6364023373390481</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.6000819069730863</v>
+        <v>-0.865137383798297</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8473</v>
+        <v>8076</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>689.5814624781327</v>
+        <v>759.2336304785372</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>50.8</v>
+        <v>25.2</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>59.99794023164745</v>
+        <v>47.33341437294168</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>34.1383393842229</v>
+        <v>20.16915012543355</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.3005834155099229</v>
+        <v>0.559717668581182</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.7147632144482721</v>
+        <v>-0.2385221231525115</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8481</v>
+        <v>8163</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>681.0650869378728</v>
+        <v>743.8912534400679</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>42.1</v>
+        <v>42.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>64.54867046426301</v>
+        <v>59.37129553812074</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>28.61258365908864</v>
+        <v>48.23176149433003</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.568177969131644</v>
+        <v>0.6098080186842006</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.1092860738915924</v>
+        <v>-0.160999852350014</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8358</v>
+        <v>8071</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>679.1057632678868</v>
+        <v>740.5861011716337</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>657</v>
+        <v>27</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>61.50723182491143</v>
+        <v>62.00720267141334</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>24.75946311702135</v>
+        <v>44.6668773597356</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.863621559834572</v>
+        <v>0.6802828435165098</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>2.213057556026499</v>
+        <v>0.3826785774719559</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>9930</v>
+        <v>8121</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>678.6791362515934</v>
+        <v>733.5628632055822</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>70.09999999999999</v>
+        <v>49</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>58.84031336378653</v>
+        <v>61.96837313635397</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>11.21844588706947</v>
+        <v>47.69460314954898</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.932249135801524</v>
+        <v>1.479167186344255</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.1325573082611716</v>
+        <v>0.6304143501546511</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8341</v>
+        <v>8112</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>673.087333471714</v>
+        <v>729.5369302930279</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>79.3</v>
+        <v>95.8</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>56.6547039151308</v>
+        <v>55.71163150780352</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>26.68957542145884</v>
+        <v>26.59203057857233</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.8590362712968133</v>
+        <v>0.8046109638442666</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.07566640600827521</v>
+        <v>0.2993059656699737</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8215</v>
+        <v>8072</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>665.8825256705372</v>
+        <v>726.6274616619258</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>30</v>
+        <v>30.6</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>52.19334585523595</v>
+        <v>61.04204286938454</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>28.01863083463742</v>
+        <v>24.97160373380225</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.4913558385413805</v>
+        <v>1.571701232284628</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.0039013290933949</v>
+        <v>0.1960233544343559</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8049</v>
+        <v>8070</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>660.2605559869041</v>
+        <v>718.462045289231</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>27.3</v>
+        <v>58.6</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>55.2231870434814</v>
+        <v>60.81457906733305</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>25.87632172149108</v>
+        <v>28.07914493098508</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.7137867423677872</v>
+        <v>1.394109889830346</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.040576107839498</v>
+        <v>-0.4432458619919051</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8097</v>
+        <v>8096</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>658.3007231672585</v>
+        <v>714.2689524713386</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>60.8</v>
+        <v>150.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>63.03241610917366</v>
+        <v>65.89018543208368</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>26.48567015739554</v>
+        <v>44.45932241164056</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.845153455738113</v>
+        <v>0.8422946702833084</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.0601396718254807</v>
+        <v>1.720895426174769</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8088</v>
+        <v>8473</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>657.1374604960097</v>
+        <v>709.5814624781327</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>68.2</v>
+        <v>50.8</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>63.52112465827569</v>
+        <v>59.99794028869673</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>27.04796478100105</v>
+        <v>34.13833924026255</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.9891587938971432</v>
+        <v>0.3005834155099229</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.5492876844673482</v>
+        <v>-0.714763214499778</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8996</v>
+        <v>8454</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>653.1475687139243</v>
+        <v>700.7486541667641</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1450</v>
+        <v>330</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>61.35451329465793</v>
+        <v>57.40891596890565</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>23.23288113062859</v>
+        <v>51.08885293321879</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.8637331837377973</v>
+        <v>0.3966337566213</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>36.40534814657968</v>
+        <v>-6.380307698989867</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8086</v>
+        <v>8481</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>642.5723024899361</v>
+        <v>681.0650869378728</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>159.5</v>
+        <v>42.1</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>52.06799751298394</v>
+        <v>64.5486706624075</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>22.03858852879184</v>
+        <v>28.61258371897543</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.7340044776158087</v>
+        <v>0.568177969131644</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>1</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.3027809379918236</v>
+        <v>0.1092860738400818</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8131</v>
+        <v>9930</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>638.2422447624508</v>
+        <v>678.6791362515935</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>74.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>56.24620870834666</v>
+        <v>58.84031343415207</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>16.75919661421779</v>
+        <v>11.21844593648084</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.046766458917964</v>
+        <v>2.932249135801524</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.4724891790448904</v>
+        <v>0.1325573083642048</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8476</v>
+        <v>8215</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>604.221073373549</v>
+        <v>675.8825256705372</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>87.1930551746633</v>
+        <v>52.19334587543065</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>50.35756467404717</v>
+        <v>28.01863085270897</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.522107337354891</v>
+        <v>0.4913558385413805</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.6526331269678562</v>
+        <v>-0.0039013291449117</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8064</v>
+        <v>8049</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>601.6304493063188</v>
+        <v>660.2605559869041</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>156</v>
+        <v>27.3</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,49 +2142,49 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>58.1153599412154</v>
+        <v>55.22318712046869</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>35.77723999994588</v>
+        <v>25.87632175505616</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.6364023373390481</v>
+        <v>0.7137867423677872</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.8651373834170784</v>
+        <v>0.0405761078291955</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8109</v>
+        <v>8996</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>600.9608635298158</v>
+        <v>653.1475687139243</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>122.5</v>
+        <v>1450</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>53.15277426971735</v>
+        <v>61.35451329465793</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>26.12788102677064</v>
+        <v>23.23288113062859</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.7668171020041588</v>
+        <v>0.8637331837377973</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.1831196074033463</v>
+        <v>36.40534814657968</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8048</v>
+        <v>8086</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>593.5930720363822</v>
+        <v>642.5723024899361</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>65.59999999999999</v>
+        <v>159.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>54.30024093540138</v>
+        <v>52.06799753147797</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>20.24212335358077</v>
+        <v>22.03858861970832</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.6747232643553024</v>
+        <v>0.7340044776158087</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.2596126075090661</v>
+        <v>0.302780937538486</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8289</v>
+        <v>8084</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>587.5764582299207</v>
+        <v>638.9228313456316</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>61.2</v>
+        <v>50</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>45.4298641966304</v>
+        <v>61.21492404553139</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>28.53039572916956</v>
+        <v>19.27118650541352</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.5484347606570178</v>
+        <v>1.499374785742561</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-1.505506804186731</v>
+        <v>0.2070595001915376</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8072</v>
+        <v>8131</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>586.6274616619229</v>
+        <v>628.2422447624508</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>30.6</v>
+        <v>74.8</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,49 +2354,49 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>61.04204257114255</v>
+        <v>56.24620871079892</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>24.97160368031004</v>
+        <v>16.7591966050571</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.571701232284628</v>
+        <v>1.046766458917964</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.1960233551349544</v>
+        <v>0.4724891790242962</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8150</v>
+        <v>8299</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>581.7141033183194</v>
+        <v>606.3749957309319</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>106.5</v>
+        <v>2430</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,49 +2407,49 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>58.94078913703267</v>
+        <v>51.23782466202523</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>28.76074721054344</v>
+        <v>14.74160770730422</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.423286842132141</v>
+        <v>0.918560273667126</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.672117088558025</v>
+        <v>-5.975932897684554</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8182</v>
+        <v>8109</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>573.5489904516652</v>
+        <v>600.9608635298158</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>47.3</v>
+        <v>122.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>51.46084087654371</v>
+        <v>53.15277427376624</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>26.38324987694136</v>
+        <v>26.12788102677064</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3227681935608106</v>
+        <v>0.7668171020041588</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.4872326438279124</v>
+        <v>0.1831196075063872</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8110</v>
+        <v>8048</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>571.5660725772533</v>
+        <v>593.5930720363822</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>58.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>54.21946479930008</v>
+        <v>54.300240985358</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>19.92856071642719</v>
+        <v>20.24212349754773</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.5872627471217886</v>
+        <v>0.6747232643553024</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.1594941621079859</v>
+        <v>0.2596126072927106</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>9105</v>
+        <v>8289</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>566.4384600422302</v>
+        <v>587.5764582299207</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>9.130000000000001</v>
+        <v>61.2</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>52.32808943767304</v>
+        <v>45.42986419833228</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>44.18312856046992</v>
+        <v>28.53039573388174</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.5187642198471959</v>
+        <v>0.5484347606570178</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.2280971419995638</v>
+        <v>-1.505506804227944</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8390</v>
+        <v>8277</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>557.7791923897609</v>
+        <v>580.4577943302612</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>113.5</v>
+        <v>10.85</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>48.70926219499025</v>
+        <v>61.62234448730099</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>24.5115725942286</v>
+        <v>30.91084865092851</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.4558294821465532</v>
+        <v>0.9926647899829484</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-1.598875043135461</v>
+        <v>-0.0595330544589673</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>9103</v>
+        <v>8182</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>544.1504451692974</v>
+        <v>573.5489904516652</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>5.34</v>
+        <v>47.3</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>48.98189214010333</v>
+        <v>51.46084087530312</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>29.49259628682477</v>
+        <v>26.38324986991016</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.2916929664188186</v>
+        <v>0.3227681935608106</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.07060985961553209</v>
+        <v>-0.4872326438176153</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8488</v>
+        <v>9105</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>521.5635722013346</v>
+        <v>566.4384600422302</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>10.4</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>53.1878802357208</v>
+        <v>52.32808946100279</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>11.96697836464333</v>
+        <v>44.18312856280428</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.3568717452351924</v>
+        <v>0.5187642198471959</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0272850078908807</v>
+        <v>-0.228097142001624</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8210</v>
+        <v>8110</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>510.0525224308171</v>
+        <v>561.5660725772533</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1310</v>
+        <v>58.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>45.02415466285611</v>
+        <v>54.21946480783708</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>19.25192023133519</v>
+        <v>19.92856070267291</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.7979103480515545</v>
+        <v>0.5872627471217886</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-20.53181534426995</v>
+        <v>0.1594941620667755</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8499</v>
+        <v>8390</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>506.2965534246763</v>
+        <v>557.7791923897609</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>312</v>
+        <v>113.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>56.59367229416853</v>
+        <v>48.7092622165622</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>16.94162368864549</v>
+        <v>24.51157266384177</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.426404703933311</v>
+        <v>0.4558294821465532</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>2.131196163206268</v>
+        <v>-1.598875043341511</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8104</v>
+        <v>9103</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>504.2243598864613</v>
+        <v>544.1504451692975</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>40.1</v>
+        <v>5.34</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>52.85702538411136</v>
+        <v>48.98189192954966</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>31.06717266583345</v>
+        <v>29.492596625767</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.4692124351729209</v>
+        <v>0.2916929664188186</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,11 +2902,11 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.1024493115654798</v>
+        <v>-0.0706098595351701</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2923,7 @@
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>502.2649354422237</v>
+        <v>522.2649354422236</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>29.8</v>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>62.60910402389672</v>
+        <v>62.60910432538705</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>17.32423348662813</v>
+        <v>17.32423351407953</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>1.300261649462139</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0525492200518207</v>
+        <v>0.0525492199590957</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2965,21 +2965,21 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>9905</v>
+        <v>8488</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>498.9580330548551</v>
+        <v>521.5635722013346</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>21</v>
+        <v>10.4</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>55.46267573307806</v>
+        <v>53.18788025154085</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>17.14107795831815</v>
+        <v>11.96697836464334</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.5937281479778218</v>
+        <v>0.3568717452351924</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0556871511838923</v>
+        <v>0.0272850078702746</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8472</v>
+        <v>8210</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>495.0880752496048</v>
+        <v>510.0525224308171</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>83.90000000000001</v>
+        <v>1310</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>52.83183399978737</v>
+        <v>45.02415468756541</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>24.81574586370139</v>
+        <v>19.25192023683176</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.0352362665995166</v>
+        <v>0.7979103480515545</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.917500762794706</v>
+        <v>-20.53181534530037</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8299</v>
+        <v>8104</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>491.3749957309319</v>
+        <v>504.2243598864613</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>2430</v>
+        <v>40.1</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,49 +3096,49 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>51.23782465791624</v>
+        <v>52.85702552295555</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>14.74160768490879</v>
+        <v>31.06717266583345</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.918560273667126</v>
+        <v>0.4692124351729209</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-5.975932897375053</v>
+        <v>-0.1024493115345648</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8050</v>
+        <v>9905</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>490.2432069677416</v>
+        <v>498.9580330548552</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>55.4</v>
+        <v>21</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>52.40667292685251</v>
+        <v>55.46267588769663</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>40.92912180108031</v>
+        <v>17.14107790476467</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.2289730639942828</v>
+        <v>0.5937281479778218</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.7425687125967033</v>
+        <v>0.0556871511632825</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8102</v>
+        <v>8472</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>489.5740438792059</v>
+        <v>495.0880752496048</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>71</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>51.44137720246125</v>
+        <v>52.83183332797027</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>10.35422832561212</v>
+        <v>24.81574623386721</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.1749299082217056</v>
+        <v>0.0352362665995166</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.6842958785203521</v>
+        <v>-0.9175007574371978</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8155</v>
+        <v>8050</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>481.2190253820245</v>
+        <v>490.2432069677416</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>388.5</v>
+        <v>55.4</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>50.29052502296679</v>
+        <v>52.40667300761992</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>17.5164289740673</v>
+        <v>40.92912183545563</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.8524233311987289</v>
+        <v>0.2289730639942828</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>2.492078303165823</v>
+        <v>-0.7425687128233704</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8383</v>
+        <v>8102</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>478.0104108183502</v>
+        <v>489.5740438792059</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>59.6</v>
+        <v>71</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>50.38583226721376</v>
+        <v>51.44137719418916</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>16.07128253167966</v>
+        <v>10.35422835903477</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.8002759405496944</v>
+        <v>0.1749299082217056</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.028058394726162</v>
+        <v>-0.68429587845853</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8240</v>
+        <v>8155</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>475.8282358189402</v>
+        <v>481.2190253820246</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>57</v>
+        <v>388.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>43.38377925235798</v>
+        <v>50.29052505460408</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>15.82236503442872</v>
+        <v>17.5164289674542</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.045439760394191</v>
+        <v>0.8524233311987289</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0341471408971212</v>
+        <v>2.492078302547702</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8069</v>
+        <v>9910</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>473.9580987944599</v>
+        <v>481.0067443841325</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>196</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>46.466466041289</v>
+        <v>42.90864312981316</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>22.13040105424878</v>
+        <v>23.48978542738199</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5658165938389305</v>
+        <v>0.3160802773237927</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-2.927727830187713</v>
+        <v>-1.560538506572832</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>9906</v>
+        <v>8383</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>欣巴巴</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>471.6189729812961</v>
+        <v>478.0104108183502</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>42.7</v>
+        <v>59.6</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>54.61806101889957</v>
+        <v>50.38583235773732</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>41.94600877907362</v>
+        <v>16.07128262028457</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.3919201778112747</v>
+        <v>0.8002759405496944</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.2525468822646839</v>
+        <v>0.0280583943861644</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8084</v>
+        <v>8240</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>468.9228313456316</v>
+        <v>475.8282358189402</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>61.21492406935504</v>
+        <v>43.38377927244353</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>19.27118647884373</v>
+        <v>15.82236503366688</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.499374785742561</v>
+        <v>1.045439760394191</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.2070595000885087</v>
+        <v>0.0341471407940852</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8277</v>
+        <v>8069</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>465.4577943302612</v>
+        <v>473.9580987944599</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>10.85</v>
+        <v>196</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>61.6223444916603</v>
+        <v>46.46646621607871</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>30.91084856788684</v>
+        <v>22.13040100783643</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.9926647899829484</v>
+        <v>0.5658165938389305</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.0595330544507243</v>
+        <v>-2.9277278322483</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>9912</v>
+        <v>9906</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>欣巴巴</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>462.5254779946099</v>
+        <v>471.6189729812961</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>12.6</v>
+        <v>42.7</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>53.6843486887205</v>
+        <v>54.61806117112484</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>23.24210201748755</v>
+        <v>41.94600893439546</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.1637310654190126</v>
+        <v>0.3919201778112747</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0075562706145754</v>
+        <v>0.2525468820174179</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8087</v>
+        <v>9912</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>441.4074154197762</v>
+        <v>462.5254779946099</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>32.9</v>
+        <v>12.6</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>43.31558781255821</v>
+        <v>53.68434864961797</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>18.25435968540868</v>
+        <v>23.24210197894435</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.4143079321973802</v>
+        <v>0.1637310654190126</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.2885733913564145</v>
+        <v>0.0075562706145754</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8422</v>
+        <v>8087</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>423.4366597815709</v>
+        <v>441.4074154197762</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>29</v>
+        <v>32.9</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>55.16474928775377</v>
+        <v>43.31558788359379</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>16.45022101854169</v>
+        <v>18.25435970065633</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5568646625253085</v>
+        <v>0.4143079321973802</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0751846492919611</v>
+        <v>-0.2885733912121742</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8093</v>
+        <v>8477</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>419.4542699271906</v>
+        <v>437.2594229051118</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>18.85</v>
+        <v>18</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>51.76021267462438</v>
+        <v>54.75082368869705</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>8.145455728452427</v>
+        <v>27.57319821365365</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.0853663416521054</v>
+        <v>0.2826355581075908</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.3993342808243402</v>
+        <v>-0.2420889010047608</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8227</v>
+        <v>8422</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>414.3347197423665</v>
+        <v>423.4366597815709</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>186.5</v>
+        <v>29</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>47.55252056227626</v>
+        <v>55.16474950103476</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>21.41072467619774</v>
+        <v>16.45022103219301</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5654184599986261</v>
+        <v>0.5568646625253085</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-2.168460102758188</v>
+        <v>0.0751846492919611</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8271</v>
+        <v>8093</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>407.0635221739278</v>
+        <v>419.45426992719</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>205.5</v>
+        <v>18.85</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>43.28342104981526</v>
+        <v>51.76021262345225</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>18.94527173738791</v>
+        <v>8.145455483789274</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.6156420877115504</v>
+        <v>0.0853663416521054</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-2.119522498787211</v>
+        <v>0.3993342810362277</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8074</v>
+        <v>8227</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>404.474185406169</v>
+        <v>414.3347197423665</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>73</v>
+        <v>186.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>47.98237038981743</v>
+        <v>47.55252061367656</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>11.54521426701848</v>
+        <v>21.41072467619775</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.027068753224825</v>
+        <v>0.5654184599986261</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.2310997711313505</v>
+        <v>-2.168460103376352</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8455</v>
+        <v>8074</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>402.6780796579882</v>
+        <v>404.474185406169</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>39.21024793481621</v>
+        <v>47.98237039180608</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>21.11941127743839</v>
+        <v>11.54521418660406</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.142854834735613</v>
+        <v>1.027068753224825</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-1.020569580188748</v>
+        <v>0.231099771121038</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8068</v>
+        <v>8455</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>391.9390224176289</v>
+        <v>402.6780796579882</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>19.35</v>
+        <v>28</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>44.30963096320023</v>
+        <v>39.21024793354282</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>21.07429304766227</v>
+        <v>21.11941127743839</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.917541205688285</v>
+        <v>1.142854834735613</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.1348633659402012</v>
+        <v>-1.020569580271169</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>9911</v>
+        <v>8271</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>371.8001224994576</v>
+        <v>392.0635221739278</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>82.59999999999999</v>
+        <v>205.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>43.63436464857219</v>
+        <v>43.283421051525</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>15.09442260063078</v>
+        <v>18.94527170431773</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.6806265468537439</v>
+        <v>0.6156420877115504</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.1361800737124519</v>
+        <v>-2.119522498715078</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>9910</v>
+        <v>8068</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>371.0067443841326</v>
+        <v>391.9390224176289</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>19.35</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>42.9086432251033</v>
+        <v>44.30963076846436</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>23.48978513601457</v>
+        <v>21.07429313014321</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.3160802773237927</v>
+        <v>0.917541205688285</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-1.56053850739707</v>
+        <v>0.1348633662183809</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8067</v>
+        <v>8411</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>362.1247911744752</v>
+        <v>380.5354675612545</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>13</v>
+        <v>11.95</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>51.38699410105697</v>
+        <v>42.74419319848481</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>6.292660065458068</v>
+        <v>35.29472882219779</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.9209847810710292</v>
+        <v>0.4767384702607667</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.1239959068500193</v>
+        <v>-0.0102356555388878</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8089</v>
+        <v>9911</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>櫻花</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>352.3103951005759</v>
+        <v>371.8001224994576</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>20.4</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>46.61600769605353</v>
+        <v>43.63436424819826</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>34.76108163047293</v>
+        <v>15.09442293705544</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.4262400846063936</v>
+        <v>0.6806265468537439</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.017412579432692</v>
+        <v>-0.1361800731972979</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8103</v>
+        <v>8464</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>339.5731876248861</v>
+        <v>365.7126636425585</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>97.40000000000001</v>
+        <v>343.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,49 +4315,49 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>44.70691195735639</v>
+        <v>54.09381939962464</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>21.13206731413157</v>
+        <v>17.3840502161888</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.550296101209379</v>
+        <v>1.246458487941021</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M73" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.2162075660894791</v>
+        <v>2.661152226174348</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8442</v>
+        <v>8067</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>336.8448476053441</v>
+        <v>362.1247911744752</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>40.55</v>
+        <v>13</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>40.82635727905032</v>
+        <v>51.38699416554926</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>21.89827073855919</v>
+        <v>6.292659880393878</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.286429133050732</v>
+        <v>0.9209847810710292</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.4614607433019853</v>
+        <v>-0.1239959070045632</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8101</v>
+        <v>8374</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>312.6832282941425</v>
+        <v>360.8012351714846</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>13.75</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>44.82269502083291</v>
+        <v>45.2384606630294</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>15.07404812772795</v>
+        <v>17.06047329348017</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5016509648299052</v>
+        <v>0.2723314549481139</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.2496876310379848</v>
+        <v>-1.136218645322259</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8183</v>
+        <v>8089</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>312.5978753445236</v>
+        <v>352.3103951005764</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>32.35</v>
+        <v>20.4</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>50.10453812044537</v>
+        <v>46.61600783395421</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>13.8786578511923</v>
+        <v>34.76108171199527</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.9480619811913542</v>
+        <v>0.4262400846063936</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.1694359308368792</v>
+        <v>0.0174125786702775</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8114</v>
+        <v>8487</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>308.4219018000724</v>
+        <v>340.6031056584428</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>207</v>
+        <v>78.8</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>43.12814158196543</v>
+        <v>46.49962471365984</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>25.59970891501981</v>
+        <v>15.36168032231745</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.7634395058788715</v>
+        <v>0.63241115645091</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-3.221063714234528</v>
+        <v>-0.2671905473652922</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8176</v>
+        <v>8103</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>305.3534311045403</v>
+        <v>339.5731876248861</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>10.05</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>43.65054714179532</v>
+        <v>44.70691199884291</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>8.666807810402311</v>
+        <v>21.13206734392218</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.029462806985472</v>
+        <v>0.550296101209379</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.0008604268700389</v>
+        <v>-0.2162075662130842</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8443</v>
+        <v>8442</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>303.4867316979008</v>
+        <v>336.8448476053441</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>11.5</v>
+        <v>40.55</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>54.91762868774698</v>
+        <v>40.82635716076975</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>53.68040583264136</v>
+        <v>21.8982708854567</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.4122407991966426</v>
+        <v>1.286429133050732</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0322383629309855</v>
+        <v>0.461460743446225</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8477</v>
+        <v>8431</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>297.2594229051118</v>
+        <v>336.4997938876605</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>54.7508236945582</v>
+        <v>48.51820173334537</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>27.57319818770709</v>
+        <v>16.2081860828396</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.2826355581075908</v>
+        <v>0.5230197345834665</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.2420889009841552</v>
+        <v>0.8803302434835989</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8147</v>
+        <v>8443</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>295.3099876453169</v>
+        <v>323.4867316979008</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>145</v>
+        <v>11.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>39.67552687874783</v>
+        <v>54.91762868774698</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>20.90596753450369</v>
+        <v>53.68040583264136</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.3177473756476709</v>
+        <v>0.4122407991966426</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-1.220855469253969</v>
+        <v>0.0322383629309855</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>9110</v>
+        <v>8101</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>281.8180061690114</v>
+        <v>312.6832282941425</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>0</v>
+        <v>13.75</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>15.99527001672097</v>
+        <v>44.82269353877335</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>18.64180333268789</v>
+        <v>15.07404813022805</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0</v>
+        <v>0.5016509648299052</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.2527515507927629</v>
+        <v>-0.2496876310894985</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>9907</v>
+        <v>8183</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>統一實</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>278.4210389788527</v>
+        <v>312.5978753445236</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>15.15</v>
+        <v>32.35</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>24.71514578221152</v>
+        <v>50.10453817834437</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>25.15629359276496</v>
+        <v>13.87865790117762</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.428851905686855</v>
+        <v>0.9480619811913542</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0799440682157733</v>
+        <v>0.1694359307441527</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8411</v>
+        <v>8114</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>270.5354675612544</v>
+        <v>308.4219018000724</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>11.95</v>
+        <v>207</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,49 +4898,49 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>42.74419322922319</v>
+        <v>43.12814168379632</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>35.29472906786312</v>
+        <v>25.59970892183627</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.4767384702607667</v>
+        <v>0.7634395058788715</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0102356555491902</v>
+        <v>-3.221063714543607</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8111</v>
+        <v>8176</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>265.7501952435061</v>
+        <v>305.3534311045403</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>55.3</v>
+        <v>10.05</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>36.36266567913383</v>
+        <v>43.65054730909745</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>27.75492923407554</v>
+        <v>8.666807833172783</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.7796426718430025</v>
+        <v>1.029462806985472</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.2560925472107631</v>
+        <v>-0.0008604269318575999</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8464</v>
+        <v>8147</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>265.7126636425585</v>
+        <v>295.3099876453169</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>343.5</v>
+        <v>145</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>54.09381927077531</v>
+        <v>39.67552687580572</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>17.38405019161562</v>
+        <v>20.90596740938838</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.246458487941021</v>
+        <v>0.3177473756476709</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>2.661152228337976</v>
+        <v>-1.220855468718213</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8482</v>
+        <v>9110</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>265.5745615466516</v>
+        <v>281.8180061690114</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>49.4</v>
+        <v>0</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>52.03121982999596</v>
+        <v>15.99527002590047</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>7.427784102563045</v>
+        <v>18.64180332853534</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.5575999274902566</v>
+        <v>0</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.1801743487657041</v>
+        <v>-0.2527515507989441</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8429</v>
+        <v>9907</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>統一實</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>263.6169617594323</v>
+        <v>278.4210389788527</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>6.35</v>
+        <v>15.15</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>42.43652851501123</v>
+        <v>24.71514578221152</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>23.35004642945175</v>
+        <v>25.15629365729293</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.536643677609937</v>
+        <v>1.428851905686855</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.015934773061375</v>
+        <v>-0.07994406820547249</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8463</v>
+        <v>8111</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>263.3224160088297</v>
+        <v>265.7501952435061</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>21.35</v>
+        <v>55.3</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>39.44939151292404</v>
+        <v>36.36266581140041</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>13.98230731607946</v>
+        <v>27.75492966636124</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.824315656721316</v>
+        <v>0.7796426718430025</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0439282126064131</v>
+        <v>-0.2560925480452929</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8213</v>
+        <v>8482</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>258.4046715807425</v>
+        <v>265.574561546652</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>37.05</v>
+        <v>49.4</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>49.83611476894181</v>
+        <v>52.03121984090115</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>13.73700953646125</v>
+        <v>7.427784122680964</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.6540539254263622</v>
+        <v>0.5575999274902566</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0354976444167235</v>
+        <v>-0.180174349116005</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8932</v>
+        <v>8429</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>253.4294427963872</v>
+        <v>263.6169617594323</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>100.5</v>
+        <v>6.35</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>50.97521094592191</v>
+        <v>42.43652869178403</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>14.06620505469196</v>
+        <v>23.35004641884675</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.6137899975030047</v>
+        <v>0.536643677609937</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.319567379743042</v>
+        <v>-0.0159347731087676</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>9904</v>
+        <v>8463</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>251.5939451487517</v>
+        <v>263.3224160088298</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>26</v>
+        <v>21.35</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>45.87053755522876</v>
+        <v>39.44939163190245</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>15.63412567950932</v>
+        <v>13.982307441445</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.9829829207334204</v>
+        <v>1.824315656721316</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0096577501752237</v>
+        <v>-0.0439282127094426</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8374</v>
+        <v>8213</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>250.8012351714846</v>
+        <v>258.4046715807425</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>90.40000000000001</v>
+        <v>37.05</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>45.23846086260021</v>
+        <v>49.83611478763765</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>17.06047327317276</v>
+        <v>13.7370095245209</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.2723314549481139</v>
+        <v>0.6540539254263622</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-1.136218647135577</v>
+        <v>0.0354976443858161</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8478</v>
+        <v>8932</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>241.7241681571049</v>
+        <v>253.4294427963872</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>152</v>
+        <v>100.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>43.45666223546137</v>
+        <v>50.97521128561966</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>15.18050058673783</v>
+        <v>14.06620506134668</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.3431269125502306</v>
+        <v>0.6137899975030047</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.2386224838832471</v>
+        <v>-0.3195673798136706</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8201</v>
+        <v>9904</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>241.5542647673434</v>
+        <v>251.5939451487517</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>13.05</v>
+        <v>26</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>46.34959719865276</v>
+        <v>45.87053750990648</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>21.48612703161893</v>
+        <v>15.63412572182796</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.4515606044512028</v>
+        <v>0.9829829207334204</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.041975795307972</v>
+        <v>0.0096577501855267</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8487</v>
+        <v>8478</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>230.6031056584428</v>
+        <v>241.7241681571049</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>78.8</v>
+        <v>152</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>46.49962470301764</v>
+        <v>43.45666234688909</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>15.36168040088902</v>
+        <v>15.18050056339591</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.63241115645091</v>
+        <v>0.3431269125502306</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.26719054734469</v>
+        <v>-0.2386224846044355</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8423</v>
+        <v>8201</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>226.6535213779775</v>
+        <v>241.5542647673434</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>17.8</v>
+        <v>13.05</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>49.26557208232486</v>
+        <v>46.34959726735994</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>12.08905192142642</v>
+        <v>21.4861270719911</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.369124521285513</v>
+        <v>0.4515606044512028</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0133296368171201</v>
+        <v>-0.0419757953903969</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8462</v>
+        <v>8423</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>221.3459551832071</v>
+        <v>226.6535213779775</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>138.5</v>
+        <v>17.8</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>43.55459282630165</v>
+        <v>49.26557219444822</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>17.49799163081332</v>
+        <v>12.08905192142642</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.8241728766516228</v>
+        <v>0.369124521285513</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.305039186755669</v>
+        <v>0.0133296368171201</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8367</v>
+        <v>8462</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>218.7790692646309</v>
+        <v>221.345955183207</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>40.45</v>
+        <v>138.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>40.10630767712123</v>
+        <v>43.55459291177165</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>23.43615286050267</v>
+        <v>17.49799169377471</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.8391522150392297</v>
+        <v>0.8241728766516228</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.07530525293116599</v>
+        <v>-0.3050391861374852</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8249</v>
+        <v>8367</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>206.6206919293584</v>
+        <v>218.7790692646309</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>51.4</v>
+        <v>40.45</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>47.30198128814829</v>
+        <v>40.10630769570793</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>17.12987036386708</v>
+        <v>23.43615299525284</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.3256837442043904</v>
+        <v>0.8391522150392297</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.1974388331675615</v>
+        <v>0.0753052530548035</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8080</v>
+        <v>8249</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>201.8355642671046</v>
+        <v>206.6206919293584</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>27.9</v>
+        <v>51.4</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>47.23998423092257</v>
+        <v>47.30198138989353</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>46.38429987890565</v>
+        <v>17.1298703469173</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.941399676689857</v>
+        <v>0.3256837442043904</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0265559124224529</v>
+        <v>-0.1974388334869447</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8940</v>
+        <v>8080</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>183.3980259817191</v>
+        <v>201.8355642671046</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>16.65</v>
+        <v>27.9</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>46.07017572683471</v>
+        <v>47.23998463911938</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>14.8776851060167</v>
+        <v>46.38429987300056</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.8298596579497132</v>
+        <v>0.941399676689857</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0571763391675099</v>
+        <v>0.0265559124224529</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>9955</v>
+        <v>8940</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>178.6393817524421</v>
+        <v>183.3980259817193</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>26.85</v>
+        <v>16.65</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>41.21029036166458</v>
+        <v>46.07017608320919</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>22.10648536135053</v>
+        <v>14.87768508945294</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.6131050925427566</v>
+        <v>0.8298596579497132</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.0115354112286019</v>
+        <v>0.0571763391262944</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8410</v>
+        <v>9955</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>178.4638398921316</v>
+        <v>178.6393817524421</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>32.35</v>
+        <v>26.85</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>32.68950704135716</v>
+        <v>41.2102904471529</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>22.4736805221894</v>
+        <v>22.10648536738217</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.246383989213159</v>
+        <v>0.6131050925427566</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.1320816510866104</v>
+        <v>0.011535411043146</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8222</v>
+        <v>8410</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>171.572241877613</v>
+        <v>178.4638398921316</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>35.5</v>
+        <v>32.35</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>48.78576827480225</v>
+        <v>32.68950702539961</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>13.53555748221636</v>
+        <v>22.47368040501516</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.766942169496679</v>
+        <v>1.246383989213159</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.051373907970501</v>
+        <v>-0.1320816512720605</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8431</v>
+        <v>8467</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>166.4997938876605</v>
+        <v>174.9444578784789</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>55</v>
+        <v>123.5</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>48.51820166689556</v>
+        <v>49.86489939571511</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>16.20818606031471</v>
+        <v>15.94770096539969</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.5230197345834665</v>
+        <v>1.283053976653244</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,11 +6082,11 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.8803302436896623</v>
+        <v>1.844114533769772</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>33.70775268838996</v>
+        <v>33.70775267945906</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>17.3022161620801</v>
+        <v>17.30221622817004</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.548270641022742</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.2062692820732866</v>
+        <v>-0.2062692821248026</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8085</v>
+        <v>8222</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>160.9294398573599</v>
+        <v>161.5722418776281</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>12.25</v>
+        <v>35.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>44.51654755585871</v>
+        <v>48.78576861268549</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>20.08022880616156</v>
+        <v>13.5355575508762</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.8700243819914563</v>
+        <v>0.766942169496679</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0631018615093616</v>
+        <v>0.0513739074553541</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8440</v>
+        <v>8085</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>157.8225104383756</v>
+        <v>160.9294398573599</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>21.8</v>
+        <v>12.25</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>42.7360636634348</v>
+        <v>44.51654768113482</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>12.41521496946988</v>
+        <v>20.08022899248008</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.3724603374130559</v>
+        <v>0.8700243819914563</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.1325498584806576</v>
+        <v>-0.0631018616329979</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8092</v>
+        <v>8440</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>154.6645241811281</v>
+        <v>157.8225104383757</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>14.1</v>
+        <v>21.8</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>31.39429074483249</v>
+        <v>42.73606368730876</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>18.27966154853917</v>
+        <v>12.41521531164536</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.6344482455999652</v>
+        <v>0.3724603374130559</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.2190501798120991</v>
+        <v>-0.1325498582230863</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8234</v>
+        <v>8092</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>149.9703243980113</v>
+        <v>154.6645241811281</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>64.3</v>
+        <v>14.1</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>45.15086646175843</v>
+        <v>31.39429078911581</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>17.05240239564467</v>
+        <v>18.27966175533177</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.55060053433783</v>
+        <v>0.6344482455999652</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.3871666432378859</v>
+        <v>-0.2190501796575573</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>9902</v>
+        <v>8234</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>147.7554039985121</v>
+        <v>149.9703243979983</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>13.6</v>
+        <v>64.3</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>42.17455023650646</v>
+        <v>45.15086653182681</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>14.12230044202125</v>
+        <v>17.05240242319484</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.073658647596305</v>
+        <v>0.55060053433783</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0001216184892246</v>
+        <v>-0.3871666436293876</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8466</v>
+        <v>9902</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>141.8325487308763</v>
+        <v>147.7554039985309</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>15.6</v>
+        <v>13.6</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>46.57420924828515</v>
+        <v>42.17455085149948</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>19.46398418278059</v>
+        <v>14.12230043682391</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.198432488371461</v>
+        <v>1.073658647596305</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0104414380961902</v>
+        <v>0.0001216184583162</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6463,21 +6463,21 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>8404</v>
+        <v>8466</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>134.2427544305237</v>
+        <v>141.8325487308763</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>44.12771894535064</v>
+        <v>46.57420928120026</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>13.26263831555288</v>
+        <v>19.46398480476622</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.6465518573085458</v>
+        <v>0.198432488371461</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0373622073233545</v>
+        <v>-0.0104414380961902</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>9802</v>
+        <v>8404</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>128.2083852854139</v>
+        <v>134.2427544305237</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>16.7</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>39.39658208387237</v>
+        <v>44.12771893280634</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>13.69876815713244</v>
+        <v>13.26263829165302</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.3982581294123505</v>
+        <v>0.6465518573085458</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.3658597103436258</v>
+        <v>-0.0373622073542619</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>8171</v>
+        <v>9802</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>108.6276292887747</v>
+        <v>128.2083852854144</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>21.45</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>40.69183114369692</v>
+        <v>39.39658193962956</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>18.2830854961379</v>
+        <v>13.69876814700841</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.5894531429303892</v>
+        <v>0.3982581294123505</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.2226680841593348</v>
+        <v>-0.3658597102405979</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>8467</v>
+        <v>8171</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>64.94445787847906</v>
+        <v>108.6276292887745</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>123.5</v>
+        <v>21.45</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>49.86489936557564</v>
+        <v>40.69183148532912</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>15.94770089903274</v>
+        <v>18.28308548723909</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.283053976653244</v>
+        <v>0.5894531429303892</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>1.844114534594008</v>
+        <v>-0.2226680843756952</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
